--- a/jogos_2024-08-26.xlsx
+++ b/jogos_2024-08-26.xlsx
@@ -1159,19 +1159,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1185,55 +1185,55 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="U6" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AC6" t="n">
         <v>1.62</v>
@@ -1248,20 +1248,20 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45530.4375</v>
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Newtown</t>
+          <t>Aberystwyth Town</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
         <v>2.5</v>
@@ -1353,44 +1353,44 @@
         <v>4.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>['13', '42', '61', '83', '87']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['10', '49']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45530.4375</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Newtown</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="M8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S8" t="n">
         <v>3.4</v>
       </c>
-      <c r="N8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
       <c r="T8" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['10', '49']</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
         <v>1.44</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45530.4375</v>
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aberystwyth Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>1.5</v>
-      </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD9" t="n">
         <v>2</v>
       </c>
-      <c r="P9" t="n">
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>2.38</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['13', '42', '61', '83', '87']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>3.25</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45530.4375</v>
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1701,55 +1701,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.2</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
         <v>1.62</v>
@@ -1764,20 +1764,20 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45530.4375</v>
@@ -1923,32 +1923,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Livyi Bereh</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chornomorets</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
         <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X12" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.2</v>
+        <v>3.56</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45530.45833333334</v>
@@ -2052,33 +2052,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Livyi Bereh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Chornomorets</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
         <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X13" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['67']</t>
-        </is>
-      </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45530.45833333334</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.95</v>
+        <v>4.33</v>
       </c>
       <c r="M14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['18']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI14" t="n">
         <v>3.2</v>
       </c>
-      <c r="N14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['54']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45530.5</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.33</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2409,20 +2409,20 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45530.5</v>
@@ -2697,29 +2697,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="U18" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['19', '74', '90+3']</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['62', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45530.52083333334</v>
@@ -2826,29 +2826,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD19" t="n">
         <v>2.4</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['19', '74', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['62', '90']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>1.33</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AH19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AI19" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['45+1']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45530.52083333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="T20" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y20" t="n">
         <v>2.63</v>
       </c>
-      <c r="U20" t="n">
+      <c r="Z20" t="n">
         <v>1.44</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2</v>
       </c>
-      <c r="AA20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['63', '83', '86']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45530.54166666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,16 +3094,16 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.05</v>
+        <v>4.5</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>1.65</v>
       </c>
       <c r="O21" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="P21" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="T21" t="n">
-        <v>3.82</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="V21" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.56</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>2.31</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.63</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['70', '86']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['63', '83', '86']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['66']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45530.54166666666</v>
@@ -3213,26 +3213,26 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.52</v>
+        <v>1.61</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>3.42</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="V22" t="n">
         <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>2.93</v>
+        <v>4.45</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.64</v>
+        <v>2.38</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['61', '77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45530.54166666666</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>SCM Gloria Buzău</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
         <v>2</v>
       </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z23" t="n">
         <v>1.65</v>
       </c>
-      <c r="O23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['70', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['27', '43']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45530.54166666666</v>
@@ -3471,35 +3471,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="O24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P24" t="n">
         <v>2.25</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.54</v>
-      </c>
       <c r="Q24" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.15</v>
       </c>
-      <c r="X24" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['16']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH24" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45530.54166666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SCM Gloria Buzău</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="O25" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="X25" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39', '76']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['27', '43']</t>
+          <t>['67', '71', '82']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45530.54166666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.25</v>
+        <v>1.53</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>1.62</v>
+        <v>5.75</v>
       </c>
       <c r="O26" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.25</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
       <c r="U26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['25', '70']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI26" t="n">
         <v>1.36</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['39', '76']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['67', '71', '82']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45530.54166666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3883,66 +3883,66 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.53</v>
+        <v>2.52</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>5.75</v>
+        <v>2.92</v>
       </c>
       <c r="O27" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="U27" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>2.93</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.5</v>
+        <v>3.64</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AC27" t="n">
         <v>1.83</v>
@@ -3952,25 +3952,25 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['25', '70']</t>
+          <t>['61', '77']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.6</v>
+        <v>1.52</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45530.54166666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,109 +3997,109 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA28" t="n">
         <v>4</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AB28" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['5', '53', '84']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45530.5625</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>4.31</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y29" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q29" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Z29" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['45', '48']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['6', '85']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45530.5625</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
         <v>1</v>
-      </c>
-      <c r="H30" t="n">
-        <v>3</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="N30" t="n">
-        <v>3.3</v>
+        <v>4.31</v>
       </c>
       <c r="O30" t="n">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>5.17</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="T30" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V30" t="n">
         <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X30" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AA30" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['45', '48']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['5', '53', '84']</t>
+          <t>['6', '85']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45530.5625</v>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Trelleborg W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.3</v>
+        <v>29</v>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N31" t="n">
-        <v>6.5</v>
+        <v>1.03</v>
       </c>
       <c r="O31" t="n">
-        <v>1.73</v>
+        <v>26</v>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.5</v>
+        <v>1.14</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="S31" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.38</v>
+        <v>5.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.55</v>
+        <v>1.67</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '25', '28', '36', '43', '57', '67', '82']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.25</v>
+        <v>10</v>
       </c>
       <c r="AJ31" t="n">
-        <v>4</v>
+        <v>1.06</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45530.58333333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trelleborg W</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>29</v>
+        <v>2.37</v>
       </c>
       <c r="M32" t="n">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="O32" t="n">
-        <v>26</v>
+        <v>3.06</v>
       </c>
       <c r="P32" t="n">
-        <v>5.5</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.14</v>
+        <v>3.06</v>
       </c>
       <c r="R32" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="T32" t="n">
-        <v>1.85</v>
+        <v>2.51</v>
       </c>
       <c r="U32" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="X32" t="n">
-        <v>8</v>
+        <v>3.92</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.67</v>
+        <v>2.64</v>
       </c>
       <c r="AB32" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['11', '25', '28', '36', '43', '57', '67', '82']</t>
+          <t>['57', '90']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>6</v>
+        <v>1.49</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="AI32" t="n">
-        <v>10</v>
+        <v>1.94</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.06</v>
+        <v>1.94</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45530.58333333334</v>
@@ -4632,35 +4632,35 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="M33" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O33" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X33" t="n">
-        <v>4.33</v>
+        <v>3.96</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="AB33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI33" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['5']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['12', '44', '50', '90']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45530.58333333334</v>
@@ -4761,119 +4761,119 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O34" t="n">
         <v>2</v>
       </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O34" t="n">
-        <v>4</v>
-      </c>
       <c r="P34" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>2.2</v>
+        <v>4.25</v>
       </c>
       <c r="T34" t="n">
-        <v>4</v>
+        <v>1.97</v>
       </c>
       <c r="U34" t="n">
-        <v>1.22</v>
+        <v>1.78</v>
       </c>
       <c r="V34" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.42</v>
+        <v>2.89</v>
       </c>
       <c r="AA34" t="n">
-        <v>5.25</v>
+        <v>1.85</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.62</v>
+        <v>2.58</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['82', '90+7']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.38</v>
+        <v>2.39</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.38</v>
+        <v>1.47</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.91</v>
+        <v>2.58</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45530.58333333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,109 +4900,109 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI35" t="n">
         <v>2.3</v>
       </c>
-      <c r="O35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>['39', '56']</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AJ35" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45530.58333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.1</v>
+        <v>6.5</v>
       </c>
       <c r="O36" t="n">
-        <v>3.75</v>
+        <v>1.73</v>
       </c>
       <c r="P36" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="X36" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>['19']</t>
-        </is>
-      </c>
       <c r="AG36" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.34</v>
+        <v>2.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.67</v>
+        <v>4</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45530.58333333334</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5173,10 +5173,10 @@
         <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="N37" t="n">
         <v>2.45</v>
       </c>
       <c r="O37" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="T37" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="U37" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="X37" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.92</v>
+        <v>5.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="AC37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD37" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['14', '29']</t>
+          <t>['82', '90+7']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45530.58333333334</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,109 +5287,109 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
         <v>2</v>
       </c>
-      <c r="I38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>2.2</v>
-      </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="O38" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P38" t="n">
         <v>2.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="R38" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="T38" t="n">
-        <v>2.63</v>
+        <v>3.22</v>
       </c>
       <c r="U38" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W38" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB38" t="n">
         <v>1.22</v>
       </c>
-      <c r="X38" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AC38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['49', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['21', '70', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>['33', '75']</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH38" t="n">
+      <c r="AI38" t="n">
         <v>1.62</v>
       </c>
-      <c r="AI38" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ38" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45530.58333333334</v>
@@ -5406,33 +5406,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
         <v>1</v>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
@@ -5442,65 +5442,65 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="O39" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="P39" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.5</v>
+        <v>2.84</v>
       </c>
       <c r="R39" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="S39" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="T39" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="U39" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W39" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
-        <v>3.96</v>
+        <v>4.8</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['39', '56']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45530.58333333334</v>
@@ -5535,33 +5535,33 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
         <v>1</v>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="M40" t="n">
         <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="O40" t="n">
-        <v>2.6</v>
+        <v>3.36</v>
       </c>
       <c r="P40" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD40" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC40" t="n">
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['9', '50', '75']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>['49', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['86']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45530.58333333334</v>
@@ -5793,29 +5793,29 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.6</v>
+        <v>1.83</v>
       </c>
       <c r="M42" t="n">
         <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="O42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q42" t="n">
         <v>4.33</v>
       </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X42" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD42" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>2.6</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>['72']</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.57</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45530.58333333334</v>
@@ -5922,30 +5922,30 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
         <v>1</v>
       </c>
-      <c r="H43" t="n">
-        <v>2</v>
-      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="O43" t="n">
-        <v>3.06</v>
+        <v>4.33</v>
       </c>
       <c r="P43" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.06</v>
+        <v>2.6</v>
       </c>
       <c r="R43" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="T43" t="n">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="V43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W43" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="X43" t="n">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.64</v>
+        <v>3.3</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ43" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>['68']</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>['57', '90']</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.94</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45530.58333333334</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,25 +6061,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6087,34 +6087,34 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="O44" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="P44" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="R44" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S44" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="T44" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="U44" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V44" t="n">
         <v>1.04</v>
@@ -6123,47 +6123,47 @@
         <v>1.18</v>
       </c>
       <c r="X44" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>['1', '45', '73']</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI44" t="n">
         <v>2</v>
       </c>
-      <c r="AA44" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AJ44" t="n">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45530.58333333334</v>
@@ -6190,25 +6190,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.75</v>
+        <v>1.48</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N45" t="n">
+        <v>5</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z45" t="n">
         <v>2.2</v>
       </c>
-      <c r="O45" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X45" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AA45" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['9', '50', '75']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '44', '50', '90']</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="AI45" t="n">
-        <v>2.09</v>
+        <v>1.4</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45530.58333333334</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,19 +6319,19 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="M46" t="n">
         <v>3.3</v>
       </c>
       <c r="N46" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="O46" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P46" t="n">
         <v>2.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="R46" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S46" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="T46" t="n">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="U46" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="V46" t="n">
         <v>1.04</v>
       </c>
       <c r="W46" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X46" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>['14', '29']</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ46" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>['56']</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>['1', '45', '73']</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.82</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45530.58333333334</v>
@@ -6438,32 +6438,32 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="n">
         <v>1</v>
-      </c>
-      <c r="H47" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="M47" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="N47" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="P47" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="R47" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S47" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>1.97</v>
+        <v>2.63</v>
       </c>
       <c r="U47" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="V47" t="n">
         <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X47" t="n">
-        <v>6.1</v>
+        <v>3.65</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.85</v>
+        <v>2.84</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['21', '70', '90+3']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['33', '75']</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.39</v>
+        <v>1.62</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.58</v>
+        <v>2.25</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45530.58333333334</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,23 +6706,23 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Şanlıurfaspor</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
         <v>2</v>
       </c>
-      <c r="I49" t="n">
-        <v>1</v>
-      </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.88</v>
+        <v>1.5</v>
       </c>
       <c r="M49" t="n">
+        <v>4</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>['14', '23', '90+6']</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ49" t="n">
         <v>3.1</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>['85', '90']</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45530.625</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,109 +7093,109 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Şanlıurfaspor</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q52" t="n">
         <v>3</v>
       </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M52" t="n">
-        <v>4</v>
-      </c>
-      <c r="N52" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O52" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>5.3</v>
-      </c>
       <c r="R52" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S52" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T52" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U52" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V52" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W52" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="X52" t="n">
-        <v>3.3</v>
+        <v>2.71</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>['85', '90']</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ52" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>['14', '23', '90+6']</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>3.1</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45530.625</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,25 +7480,25 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -7506,83 +7506,83 @@
         </is>
       </c>
       <c r="L55" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N55" t="n">
+        <v>6</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>6</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S55" t="n">
         <v>2.5</v>
       </c>
-      <c r="M55" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="O55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.63</v>
-      </c>
       <c r="T55" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U55" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V55" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W55" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X55" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Z55" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD55" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['23', '48']</t>
+          <t>['44', '55', '90+3']</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>['45+1', '90+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.45</v>
+        <v>2.07</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AJ55" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45530.65625</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -7635,65 +7635,65 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N56" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="O56" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="P56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC56" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" t="n">
-        <v>5</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X56" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD56" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>['54', '57', '84']</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -7702,16 +7702,16 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AH56" t="n">
-        <v>2.7</v>
+        <v>1.55</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AJ56" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45530.65625</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,25 +7738,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="M57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X57" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA57" t="n">
         <v>3.6</v>
       </c>
-      <c r="N57" t="n">
-        <v>6</v>
-      </c>
-      <c r="O57" t="n">
+      <c r="AB57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>['23', '48']</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>['45+1', '90+6']</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ57" t="n">
         <v>2.2</v>
-      </c>
-      <c r="P57" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>6</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T57" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>['44', '55', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>3.75</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45530.65625</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,25 +7996,25 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -8022,22 +8022,22 @@
         </is>
       </c>
       <c r="L59" t="n">
+        <v>4</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O59" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P59" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q59" t="n">
         <v>2.3</v>
-      </c>
-      <c r="M59" t="n">
-        <v>3</v>
-      </c>
-      <c r="N59" t="n">
-        <v>3</v>
-      </c>
-      <c r="O59" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>3.75</v>
       </c>
       <c r="R59" t="n">
         <v>1.44</v>
@@ -8046,59 +8046,59 @@
         <v>2.63</v>
       </c>
       <c r="T59" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U59" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V59" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W59" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="X59" t="n">
-        <v>2.4</v>
+        <v>3.06</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AA59" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AB59" t="n">
         <v>1.25</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '39', '53']</t>
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.33</v>
+        <v>2.14</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="AJ59" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45530.65625</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8269,7 +8269,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -8280,65 +8280,65 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="M61" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O61" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P61" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q61" t="n">
         <v>3.75</v>
       </c>
       <c r="R61" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S61" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="T61" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U61" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V61" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="W61" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X61" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AA61" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AC61" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>['3']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -8347,16 +8347,16 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AJ61" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45530.65625</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,25 +8383,25 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -8409,83 +8409,83 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="M62" t="n">
         <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="O62" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="P62" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="R62" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S62" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T62" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U62" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V62" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W62" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X62" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AA62" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AB62" t="n">
         <v>1.25</v>
       </c>
       <c r="AC62" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
+          <t>['54', '57', '84']</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>['28', '39', '53']</t>
-        </is>
-      </c>
       <c r="AG62" t="n">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.18</v>
+        <v>2.7</v>
       </c>
       <c r="AI62" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ62" t="n">
         <v>3.1</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>1.44</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45530.65625</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,22 +8512,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G63" t="n">
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -8538,83 +8538,83 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="M63" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P63" t="n">
         <v>2.2</v>
       </c>
-      <c r="O63" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P63" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q63" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R63" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S63" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="T63" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U63" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V63" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W63" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X63" t="n">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="Y63" t="n">
         <v>1.95</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AA63" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>['90+6']</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.27</v>
+        <v>1.9</v>
       </c>
       <c r="AI63" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AJ63" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45530.66666666666</v>
@@ -8631,35 +8631,35 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -8667,83 +8667,83 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="M64" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N64" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="O64" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="P64" t="n">
         <v>2.05</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="R64" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X64" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
         <v>1.57</v>
       </c>
-      <c r="S64" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T64" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X64" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>['25', '49', '67', '74', '78']</t>
-        </is>
-      </c>
-      <c r="AG64" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH64" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AI64" t="n">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="AJ64" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45530.66666666666</v>
@@ -8760,35 +8760,35 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Central Córdoba SdE</t>
+          <t>GOŠK Gabela</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="M65" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="O65" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P65" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="R65" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S65" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="T65" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U65" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V65" t="n">
         <v>1.07</v>
       </c>
       <c r="W65" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="X65" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.88</v>
+        <v>2.14</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AA65" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AC65" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8859,20 +8859,20 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AJ65" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45530.66666666666</v>
@@ -8889,26 +8889,26 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Central Córdoba SdE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -8925,83 +8925,83 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="M66" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="N66" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="O66" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X66" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG66" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ66" t="n">
         <v>2.3</v>
-      </c>
-      <c r="P66" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S66" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T66" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X66" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>['90+6']</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG66" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>3</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45530.66666666666</v>
@@ -9018,29 +9018,29 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>GOŠK Gabela</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -9054,83 +9054,83 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.66</v>
+        <v>4.5</v>
       </c>
       <c r="M67" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>2.53</v>
+        <v>1.85</v>
       </c>
       <c r="O67" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="P67" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X67" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC67" t="n">
         <v>2</v>
       </c>
-      <c r="Q67" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S67" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T67" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X67" t="n">
+      <c r="AD67" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>['25', '49', '67', '74', '78']</t>
+        </is>
+      </c>
+      <c r="AG67" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI67" t="n">
         <v>2.88</v>
       </c>
-      <c r="Y67" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AG67" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AJ67" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45530.66666666666</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,109 +9286,109 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
         <v>2</v>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>1.85</v>
-      </c>
       <c r="M69" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N69" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="O69" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="P69" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="R69" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="S69" t="n">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="T69" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="U69" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="V69" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W69" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="X69" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AA69" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>['26', '60', '64', '90+10']</t>
+          <t>['52', '90+8']</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>['12', '31', '80']</t>
+          <t>['76', '80']</t>
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AJ69" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>45530.6875</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,109 +9415,109 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G70" t="n">
+        <v>4</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
         <v>2</v>
       </c>
-      <c r="H70" t="n">
-        <v>2</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="M70" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O70" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P70" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S70" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X70" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA70" t="n">
         <v>3.1</v>
       </c>
-      <c r="N70" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O70" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P70" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R70" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S70" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T70" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U70" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V70" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W70" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X70" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AB70" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AC70" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>['52', '90+8']</t>
+          <t>['26', '60', '64', '90+10']</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>['76', '80']</t>
+          <t>['12', '31', '80']</t>
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AJ70" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AK70" s="3" t="n">
         <v>45530.6875</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,16 +9544,16 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Atlético Tucumán</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -9570,49 +9570,49 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="M71" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="N71" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O71" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P71" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R71" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S71" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T71" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U71" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V71" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="W71" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="X71" t="n">
         <v>2.25</v>
       </c>
       <c r="Y71" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AA71" t="n">
         <v>5.5</v>
@@ -9621,14 +9621,14 @@
         <v>1.11</v>
       </c>
       <c r="AC71" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AD71" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -9637,16 +9637,16 @@
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AJ71" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>45530.77083333334</v>
@@ -9673,19 +9673,19 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Atlético Tucumán</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -9699,80 +9699,80 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="M72" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="N72" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O72" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P72" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Q72" t="n">
         <v>4.33</v>
       </c>
       <c r="R72" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S72" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X72" t="n">
         <v>2.25</v>
       </c>
-      <c r="T72" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U72" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V72" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W72" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X72" t="n">
-        <v>2.45</v>
-      </c>
       <c r="Y72" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AA72" t="n">
-        <v>4.85</v>
+        <v>5.5</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
           <t>[]</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>['89']</t>
         </is>
       </c>
       <c r="AG72" t="n">
         <v>1.33</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AJ72" t="n">
         <v>2.6</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,19 +9802,19 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -9831,7 +9831,7 @@
         <v>2.25</v>
       </c>
       <c r="M73" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N73" t="n">
         <v>3.5</v>
@@ -9840,10 +9840,10 @@
         <v>3.1</v>
       </c>
       <c r="P73" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q73" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R73" t="n">
         <v>1.57</v>
@@ -9858,25 +9858,25 @@
         <v>1.25</v>
       </c>
       <c r="V73" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W73" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="X73" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA73" t="n">
-        <v>5.5</v>
+        <v>4.85</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AC73" t="n">
         <v>2.1</v>
@@ -9891,20 +9891,20 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ73" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AK73" s="3" t="n">
         <v>45530.77083333334</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,25 +10189,25 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -10215,83 +10215,83 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="M76" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N76" t="n">
+        <v>4</v>
+      </c>
+      <c r="O76" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S76" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T76" t="n">
         <v>3.5</v>
       </c>
-      <c r="O76" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P76" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>4</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S76" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T76" t="n">
-        <v>3.25</v>
-      </c>
       <c r="U76" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V76" t="n">
         <v>1.07</v>
       </c>
       <c r="W76" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X76" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AA76" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>['68', '86']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH76" t="n">
         <v>1.7</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AK76" s="3" t="n">
         <v>45530.875</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,19 +10318,19 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="G77" t="n">
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -10344,34 +10344,34 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="M77" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="N77" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="P77" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="R77" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S77" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T77" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U77" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V77" t="n">
         <v>1.07</v>
@@ -10380,19 +10380,19 @@
         <v>1.5</v>
       </c>
       <c r="X77" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AA77" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AC77" t="n">
         <v>2.25</v>
@@ -10402,25 +10402,25 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AJ77" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK77" s="3" t="n">
         <v>45530.875</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,16 +10447,16 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
@@ -10465,7 +10465,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -10473,83 +10473,83 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="M78" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="N78" t="n">
         <v>3.5</v>
       </c>
       <c r="O78" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P78" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>4</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S78" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T78" t="n">
         <v>3.25</v>
       </c>
-      <c r="P78" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R78" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S78" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T78" t="n">
-        <v>3.75</v>
-      </c>
       <c r="U78" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V78" t="n">
         <v>1.07</v>
       </c>
       <c r="W78" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="X78" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AA78" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AC78" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['68', '86']</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AG78" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AJ78" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AK78" s="3" t="n">
         <v>45530.875</v>

--- a/jogos_2024-08-26.xlsx
+++ b/jogos_2024-08-26.xlsx
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Aberystwyth Town</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="R6" t="n">
         <v>1.33</v>
@@ -1209,59 +1209,59 @@
         <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '42', '61', '83', '87']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.42</v>
+        <v>2.35</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.73</v>
+        <v>3.25</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45530.4375</v>
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aberystwyth Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N7" t="n">
-        <v>5.5</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>4.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['13', '42', '61', '83', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.36</v>
+        <v>2.88</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45530.4375</v>
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Newtown</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>2.45</v>
-      </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S8" t="n">
         <v>3</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['10', '49']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45530.4375</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,28 +1572,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O9" t="n">
         <v>3.25</v>
       </c>
-      <c r="O9" t="n">
-        <v>2.6</v>
-      </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
         <v>2.63</v>
@@ -1602,53 +1602,53 @@
         <v>1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45530.4375</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Newtown</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X10" t="n">
         <v>4.2</v>
       </c>
-      <c r="N10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="Y10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['10', '49']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI10" t="n">
         <v>2.05</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45530.4375</v>
@@ -2697,29 +2697,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.4</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['19', '74', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['62', '90']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.33</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AH18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['45+1']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45530.52083333334</v>
@@ -2826,29 +2826,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="U19" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X19" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['19', '74', '90+3']</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['62', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45530.52083333334</v>
@@ -2955,26 +2955,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="P20" t="n">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>2.22</v>
+        <v>3.42</v>
       </c>
       <c r="T20" t="n">
-        <v>3.82</v>
+        <v>2.35</v>
       </c>
       <c r="U20" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="V20" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>2.31</v>
+        <v>4.45</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.63</v>
+        <v>1.55</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.3</v>
+        <v>2.38</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.11</v>
+        <v>1.49</v>
       </c>
       <c r="AC20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH20" t="n">
         <v>2</v>
       </c>
-      <c r="AD20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['63', '83', '86']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['66']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AI20" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45530.54166666666</v>
@@ -3213,26 +3213,26 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -3241,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="S22" t="n">
-        <v>3.42</v>
+        <v>2.22</v>
       </c>
       <c r="T22" t="n">
-        <v>2.35</v>
+        <v>3.82</v>
       </c>
       <c r="U22" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.56</v>
       </c>
       <c r="X22" t="n">
-        <v>4.45</v>
+        <v>2.31</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.55</v>
+        <v>2.63</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.38</v>
+        <v>5.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.29</v>
+        <v>1.73</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63', '83', '86']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AH22" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45530.54166666666</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SCM Gloria Buzău</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z23" t="n">
         <v>2</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AA23" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['27', '43']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.8</v>
+        <v>1.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>2.15</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.45</v>
+        <v>1.4</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.68</v>
+        <v>3.25</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45530.54166666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,81 +3481,81 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.53</v>
+        <v>2.52</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>5.25</v>
+        <v>2.92</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="T24" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="X24" t="n">
-        <v>3.6</v>
+        <v>2.93</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.9</v>
+        <v>3.64</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC24" t="n">
         <v>1.83</v>
@@ -3565,25 +3565,25 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['61', '77']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45530.54166666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>SCM Gloria Buzău</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>5.75</v>
+        <v>1.95</v>
       </c>
       <c r="O26" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['25', '70']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['27', '43']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.13</v>
+        <v>1.8</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.6</v>
+        <v>1.24</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.36</v>
+        <v>2.45</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.4</v>
+        <v>1.68</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45530.54166666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3883,10 +3883,10 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,55 +3894,55 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.52</v>
+        <v>1.53</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.92</v>
+        <v>5.75</v>
       </c>
       <c r="O27" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="X27" t="n">
-        <v>2.93</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.64</v>
+        <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="AC27" t="n">
         <v>1.83</v>
@@ -3952,25 +3952,25 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['61', '77']</t>
+          <t>['25', '70']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.52</v>
+        <v>2.6</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45530.54166666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
         <v>1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>4.31</v>
       </c>
       <c r="O28" t="n">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.75</v>
+        <v>5.17</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="T28" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V28" t="n">
         <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X28" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AA28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['45', '48']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['5', '53', '84']</t>
+          <t>['6', '85']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45530.5625</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,109 +4126,109 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="I29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA29" t="n">
         <v>4</v>
       </c>
-      <c r="R29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AB29" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['5', '53', '84']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45530.5625</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>4.31</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q30" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Z30" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['45', '48']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['6', '85']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45530.5625</v>
@@ -4384,109 +4384,109 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trelleborg W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M31" t="n">
         <v>5</v>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>29</v>
-      </c>
-      <c r="M31" t="n">
-        <v>10</v>
-      </c>
       <c r="N31" t="n">
-        <v>1.03</v>
+        <v>6.5</v>
       </c>
       <c r="O31" t="n">
-        <v>26</v>
+        <v>1.73</v>
       </c>
       <c r="P31" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.14</v>
+        <v>6.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.5</v>
+        <v>2.38</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.67</v>
+        <v>2.55</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['11', '25', '28', '36', '43', '57', '67', '82']</t>
-        </is>
-      </c>
       <c r="AG31" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>1.25</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.06</v>
+        <v>4</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45530.58333333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
         <v>1</v>
       </c>
-      <c r="H32" t="n">
-        <v>2</v>
-      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="O32" t="n">
-        <v>3.06</v>
+        <v>3.75</v>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.06</v>
+        <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="X32" t="n">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>1.67</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['68']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['57', '90']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.94</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45530.58333333334</v>
@@ -4632,35 +4632,35 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N33" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="P33" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T33" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['12', '44', '50', '90']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH33" t="n">
         <v>2.5</v>
       </c>
-      <c r="U33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="AI33" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45530.58333333334</v>
@@ -4761,26 +4761,26 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -4789,7 +4789,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="O34" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="P34" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="S34" t="n">
-        <v>4.25</v>
+        <v>2.76</v>
       </c>
       <c r="T34" t="n">
-        <v>1.97</v>
+        <v>3.22</v>
       </c>
       <c r="U34" t="n">
-        <v>1.78</v>
+        <v>1.34</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="X34" t="n">
-        <v>6.1</v>
+        <v>2.88</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.89</v>
+        <v>1.7</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.85</v>
+        <v>3.65</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.58</v>
+        <v>1.91</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['49', '90+2']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45530.58333333334</v>
@@ -4890,35 +4890,35 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
         <v>1</v>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="N35" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S35" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3</v>
-      </c>
       <c r="T35" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="U35" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="V35" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="W35" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="X35" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.12</v>
+        <v>5.25</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['82', '90+7']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45530.58333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M36" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="N36" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="O36" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S36" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="U36" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.38</v>
+        <v>2.89</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.83</v>
+        <v>2.58</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AJ36" t="n">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45530.58333333334</v>
@@ -5148,119 +5148,119 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Trelleborg W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
+        <v>8</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>29</v>
+      </c>
+      <c r="M37" t="n">
+        <v>10</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O37" t="n">
+        <v>26</v>
+      </c>
+      <c r="P37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X37" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB37" t="n">
         <v>2</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O37" t="n">
-        <v>4</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T37" t="n">
-        <v>4</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.15</v>
       </c>
       <c r="AC37" t="n">
         <v>2.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['82', '90+7']</t>
+          <t>['11', '25', '28', '36', '43', '57', '67', '82']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.48</v>
+        <v>6</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.38</v>
+        <v>10</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.91</v>
+        <v>1.06</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45530.58333333334</v>
@@ -5277,35 +5277,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
         <v>2</v>
       </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="M38" t="n">
         <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="O38" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="P38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD38" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q38" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['49', '90+2']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>['14', '29']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45530.58333333334</v>
@@ -5406,32 +5406,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="M39" t="n">
         <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="O39" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X39" t="n">
         <v>3.2</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X39" t="n">
-        <v>4.8</v>
-      </c>
       <c r="Y39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.57</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['39', '56']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.85</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45530.58333333334</v>
@@ -5535,35 +5535,35 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P40" t="n">
         <v>2.2</v>
       </c>
-      <c r="O40" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.28</v>
-      </c>
       <c r="Q40" t="n">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="R40" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S40" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="U40" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V40" t="n">
         <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X40" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['9', '50', '75']</t>
+          <t>['21', '70', '90+3']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '75']</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AI40" t="n">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45530.58333333334</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,22 +5803,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="O42" t="n">
-        <v>2.4</v>
+        <v>3.36</v>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.33</v>
+        <v>3.02</v>
       </c>
       <c r="R42" t="n">
         <v>1.33</v>
       </c>
       <c r="S42" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T42" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="U42" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="V42" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="X42" t="n">
-        <v>4.05</v>
+        <v>3.56</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AD42" t="n">
         <v>2.2</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
+          <t>['9', '50', '75']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG42" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AH42" t="n">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45530.58333333334</v>
@@ -5922,33 +5922,33 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>1</v>
       </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="M43" t="n">
         <v>3.5</v>
       </c>
       <c r="N43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>['39', '56']</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AJ43" t="n">
         <v>1.85</v>
-      </c>
-      <c r="O43" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>['72']</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.57</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45530.58333333334</v>
@@ -6051,35 +6051,35 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G44" t="n">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ44" t="n">
         <v>2.75</v>
-      </c>
-      <c r="M44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X44" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>['56']</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>['1', '45', '73']</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.82</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45530.58333333334</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,109 +6190,109 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z45" t="n">
         <v>2</v>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M45" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N45" t="n">
-        <v>5</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X45" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z45" t="n">
+      <c r="AA45" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD45" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA45" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>['12', '44', '50', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45530.58333333334</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,19 +6319,19 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="M46" t="n">
         <v>3.3</v>
       </c>
       <c r="N46" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="O46" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P46" t="n">
         <v>2.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="R46" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="T46" t="n">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="U46" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="V46" t="n">
         <v>1.04</v>
       </c>
       <c r="W46" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X46" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['14', '29']</t>
+          <t>['1', '45', '73']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45530.58333333334</v>
@@ -6438,35 +6438,35 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="O47" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="P47" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.6</v>
+        <v>3.06</v>
       </c>
       <c r="R47" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T47" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="U47" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="V47" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W47" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X47" t="n">
-        <v>3.65</v>
+        <v>3.92</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.84</v>
+        <v>2.64</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AD47" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['21', '70', '90+3']</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['33', '75']</t>
+          <t>['57', '90']</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45530.58333333334</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,109 +6835,109 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q50" t="n">
         <v>3</v>
       </c>
-      <c r="H50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M50" t="n">
-        <v>4</v>
-      </c>
-      <c r="N50" t="n">
-        <v>3</v>
-      </c>
-      <c r="O50" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P50" t="n">
+      <c r="R50" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S50" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q50" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S50" t="n">
-        <v>4.2</v>
-      </c>
       <c r="T50" t="n">
-        <v>2.02</v>
+        <v>3.22</v>
       </c>
       <c r="U50" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="V50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W50" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="X50" t="n">
-        <v>6.5</v>
+        <v>2.71</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.38</v>
+        <v>2.2</v>
       </c>
       <c r="Z50" t="n">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.98</v>
+        <v>4.05</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.86</v>
+        <v>1.18</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AD50" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['55', '70', '85']</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['85', '90']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45530.625</v>
@@ -6964,25 +6964,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N51" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P51" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S51" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T51" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="U51" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="V51" t="n">
         <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X51" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55', '70', '85']</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>['27', '85']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AJ51" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45530.625</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,109 +7093,109 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>2</v>
       </c>
       <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
         <v>1</v>
       </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.88</v>
+        <v>2.17</v>
       </c>
       <c r="M52" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N52" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="O52" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R52" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="S52" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="T52" t="n">
-        <v>3.22</v>
+        <v>2.13</v>
       </c>
       <c r="U52" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="V52" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="X52" t="n">
-        <v>2.71</v>
+        <v>5.5</v>
       </c>
       <c r="Y52" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA52" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z52" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>4.05</v>
-      </c>
       <c r="AB52" t="n">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['85', '90']</t>
+          <t>['27', '85']</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="AI52" t="n">
-        <v>2.38</v>
+        <v>1.76</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45530.625</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,16 +7480,16 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -7506,28 +7506,28 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="M55" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="O55" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="P55" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="R55" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S55" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T55" t="n">
         <v>3.5</v>
@@ -7536,35 +7536,35 @@
         <v>1.29</v>
       </c>
       <c r="V55" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W55" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="X55" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AA55" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['44', '55', '90+3']</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -7573,16 +7573,16 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="AH55" t="n">
-        <v>2.07</v>
+        <v>1.55</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AJ55" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45530.65625</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7624,7 +7624,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -7635,65 +7635,65 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="M56" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N56" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O56" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P56" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q56" t="n">
         <v>3.75</v>
       </c>
       <c r="R56" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S56" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="T56" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U56" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V56" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="W56" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X56" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AA56" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AC56" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>['3']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -7702,16 +7702,16 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AJ56" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45530.65625</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7753,7 +7753,7 @@
         <v>2</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
         <v>1</v>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="M57" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N57" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="O57" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['23', '48']</t>
+          <t>['59', '86']</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>['45+1', '90+6']</t>
+          <t>['38', '82']</t>
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45530.65625</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,109 +7867,109 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
         <v>2</v>
       </c>
-      <c r="H58" t="n">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>4</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O58" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X58" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC58" t="n">
         <v>2</v>
       </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M58" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N58" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['59', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>['38', '82']</t>
+          <t>['28', '39', '53']</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45530.65625</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,25 +7996,25 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>4</v>
+        <v>1.57</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N59" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="O59" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="P59" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="R59" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S59" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T59" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U59" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V59" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W59" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="X59" t="n">
-        <v>3.06</v>
+        <v>2.75</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Z59" t="n">
         <v>1.67</v>
       </c>
       <c r="AA59" t="n">
-        <v>3.52</v>
+        <v>4.8</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AC59" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
+          <t>['44', '55', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>['28', '39', '53']</t>
-        </is>
-      </c>
       <c r="AG59" t="n">
-        <v>2.14</v>
+        <v>1.1</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.18</v>
+        <v>2.07</v>
       </c>
       <c r="AI59" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1.44</v>
+        <v>3.75</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45530.65625</v>
@@ -8254,16 +8254,16 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -8280,49 +8280,49 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="O61" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="P61" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="R61" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S61" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T61" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U61" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V61" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W61" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="X61" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AA61" t="n">
         <v>3.6</v>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['54', '57', '84']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -8347,16 +8347,16 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.33</v>
+        <v>1.03</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.51</v>
+        <v>2.7</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AJ61" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45530.65625</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,25 +8383,25 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -8409,49 +8409,49 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N62" t="n">
-        <v>4.5</v>
+        <v>2.63</v>
       </c>
       <c r="O62" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="P62" t="n">
         <v>2</v>
       </c>
       <c r="Q62" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="R62" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S62" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T62" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U62" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V62" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W62" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="X62" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AA62" t="n">
         <v>3.6</v>
@@ -8460,32 +8460,32 @@
         <v>1.25</v>
       </c>
       <c r="AC62" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>['23', '48']</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>['45+1', '90+6']</t>
+        </is>
+      </c>
+      <c r="AG62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ62" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>['54', '57', '84']</t>
-        </is>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG62" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>3.1</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45530.65625</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,25 +8512,25 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>GOŠK Gabela</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
         <v>1</v>
       </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -8538,83 +8538,83 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.7</v>
+        <v>2.66</v>
       </c>
       <c r="M63" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O63" t="n">
         <v>3.4</v>
       </c>
-      <c r="N63" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O63" t="n">
-        <v>2.3</v>
-      </c>
       <c r="P63" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X63" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AG63" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI63" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q63" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S63" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T63" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X63" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>['90+6']</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG63" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ63" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45530.66666666666</v>
@@ -8631,119 +8631,119 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>5</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
         <v>1</v>
       </c>
-      <c r="H64" t="n">
-        <v>1</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="M64" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N64" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="O64" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="P64" t="n">
         <v>2.05</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R64" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="S64" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="T64" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="U64" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="V64" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W64" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="X64" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AA64" t="n">
-        <v>3.3</v>
+        <v>5.31</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['25', '49', '67', '74', '78']</t>
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AI64" t="n">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="AJ64" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45530.66666666666</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,25 +8770,25 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>GOŠK Gabela</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8796,83 +8796,83 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="M65" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="O65" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P65" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R65" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S65" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="T65" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="U65" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V65" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W65" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="X65" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AA65" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AI65" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AJ65" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45530.66666666666</v>
@@ -9018,35 +9018,35 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -9054,83 +9054,83 @@
         </is>
       </c>
       <c r="L67" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N67" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O67" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q67" t="n">
         <v>4.5</v>
       </c>
-      <c r="M67" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N67" t="n">
+      <c r="R67" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X67" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z67" t="n">
         <v>1.85</v>
       </c>
-      <c r="O67" t="n">
-        <v>5</v>
-      </c>
-      <c r="P67" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S67" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T67" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W67" t="n">
+      <c r="AA67" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>['90+6']</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG67" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI67" t="n">
         <v>1.5</v>
       </c>
-      <c r="X67" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>['25', '49', '67', '74', '78']</t>
-        </is>
-      </c>
-      <c r="AG67" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AJ67" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45530.66666666666</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,109 +9286,109 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G69" t="n">
+        <v>4</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
         <v>2</v>
       </c>
-      <c r="H69" t="n">
-        <v>2</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="M69" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N69" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O69" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P69" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X69" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA69" t="n">
         <v>3.1</v>
       </c>
-      <c r="N69" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O69" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P69" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R69" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S69" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T69" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U69" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V69" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W69" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X69" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AB69" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AC69" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>['52', '90+8']</t>
+          <t>['26', '60', '64', '90+10']</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>['76', '80']</t>
+          <t>['12', '31', '80']</t>
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AJ69" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>45530.6875</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,109 +9415,109 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
         <v>2</v>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>1.85</v>
-      </c>
       <c r="M70" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N70" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="O70" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="P70" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="R70" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="S70" t="n">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="T70" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="U70" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="V70" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W70" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="X70" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AA70" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>['26', '60', '64', '90+10']</t>
+          <t>['52', '90+8']</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>['12', '31', '80']</t>
+          <t>['76', '80']</t>
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AJ70" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AK70" s="3" t="n">
         <v>45530.6875</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,19 +9544,19 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -9573,7 +9573,7 @@
         <v>2.25</v>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N71" t="n">
         <v>3.5</v>
@@ -9582,10 +9582,10 @@
         <v>3.1</v>
       </c>
       <c r="P71" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R71" t="n">
         <v>1.57</v>
@@ -9600,25 +9600,25 @@
         <v>1.25</v>
       </c>
       <c r="V71" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W71" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="X71" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA71" t="n">
-        <v>5.5</v>
+        <v>4.85</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AC71" t="n">
         <v>2.1</v>
@@ -9633,20 +9633,20 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ71" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>45530.77083333334</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,16 +9673,16 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Atlético Tucumán</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -9699,49 +9699,49 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="M72" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O72" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P72" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R72" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S72" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T72" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U72" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V72" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="W72" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="X72" t="n">
         <v>2.25</v>
       </c>
       <c r="Y72" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AA72" t="n">
         <v>5.5</v>
@@ -9750,14 +9750,14 @@
         <v>1.11</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -9766,16 +9766,16 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AJ72" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AK72" s="3" t="n">
         <v>45530.77083333334</v>
@@ -9802,19 +9802,19 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Atlético Tucumán</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -9828,80 +9828,80 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="M73" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="N73" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O73" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P73" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Q73" t="n">
         <v>4.33</v>
       </c>
       <c r="R73" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S73" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T73" t="n">
+        <v>4</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W73" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X73" t="n">
         <v>2.25</v>
       </c>
-      <c r="T73" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U73" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V73" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W73" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X73" t="n">
-        <v>2.45</v>
-      </c>
       <c r="Y73" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AA73" t="n">
-        <v>4.85</v>
+        <v>5.5</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
           <t>[]</t>
-        </is>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>['89']</t>
         </is>
       </c>
       <c r="AG73" t="n">
         <v>1.33</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AJ73" t="n">
         <v>2.6</v>
